--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="D3">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E3">
         <v>8</v>
       </c>
       <c r="G3">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H3">
         <v>426</v>
